--- a/Assets/Data/Excel/npc.xlsx
+++ b/Assets/Data/Excel/npc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cube\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1307404-EAA9-434C-A250-F233DDFB8282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B16B846-B0C6-414F-8739-6443521E7EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,10 +117,10 @@
     <t>出售基础道具的商人。</t>
   </si>
   <si>
-    <t>Assets/Arts/Character/Pirate_Male.prefab</t>
-  </si>
-  <si>
     <t>Assets/Arts/Character/Elf.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Character/Pirate/Pirate_Male.prefab</t>
   </si>
 </sst>
 </file>
@@ -497,7 +497,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" s="2">
         <v>2</v>
@@ -524,7 +524,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2">
         <v>3.5</v>
@@ -551,7 +551,7 @@
         <v>4</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>

--- a/Assets/Data/Excel/npc.xlsx
+++ b/Assets/Data/Excel/npc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cube\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B16B846-B0C6-414F-8739-6443521E7EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3C4439-97A4-440C-B117-69B627BBAC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -121,13 +121,41 @@
   </si>
   <si>
     <t>Assets/Arts/Character/Pirate/Pirate_Male.prefab</t>
+  </si>
+  <si>
+    <t>modelScale</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>模型scale</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attackRange    </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>attackInterval</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击范围</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击间隔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -146,6 +174,14 @@
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -175,12 +211,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -350,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -359,11 +398,14 @@
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="8" max="8" width="16.75" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="25.75" customWidth="1"/>
+    <col min="11" max="11" width="17.25" customWidth="1"/>
+    <col min="12" max="12" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30">
+    <row r="1" spans="1:12" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -391,8 +433,17 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" ht="15">
+    <row r="2" spans="1:12" ht="15">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -420,8 +471,17 @@
       <c r="I2" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="J2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" ht="15">
+    <row r="3" spans="1:12" ht="15">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -449,8 +509,17 @@
       <c r="I3" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="J3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" ht="15">
+    <row r="4" spans="1:12" ht="15">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -478,8 +547,17 @@
       <c r="I4" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="J4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:12">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1001</v>
@@ -505,8 +583,17 @@
       <c r="I5" s="2">
         <v>1</v>
       </c>
+      <c r="J5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:12">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>1002</v>
@@ -532,8 +619,17 @@
       <c r="I6" s="2">
         <v>1</v>
       </c>
+      <c r="J6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:12">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>2001</v>
@@ -558,6 +654,15 @@
       </c>
       <c r="I7" s="2">
         <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Excel/npc.xlsx
+++ b/Assets/Data/Excel/npc.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cube\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3C4439-97A4-440C-B117-69B627BBAC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E62F22F0-6FB8-4BAE-B4F1-67639D4600D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="npc" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -148,6 +159,17 @@
   </si>
   <si>
     <t>攻击间隔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">maxHp    </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rewardGold</t>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -389,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -405,7 +427,7 @@
     <col min="12" max="12" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17.25" customHeight="1">
+    <row r="1" spans="1:14" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -442,8 +464,14 @@
       <c r="L1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" ht="15">
+    <row r="2" spans="1:14" ht="15">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -480,8 +508,14 @@
       <c r="L2" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="M2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" ht="15">
+    <row r="3" spans="1:14" ht="15">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -518,8 +552,14 @@
       <c r="L3" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="M3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" ht="15">
+    <row r="4" spans="1:14" ht="15">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -556,8 +596,14 @@
       <c r="L4" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="M4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:14">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1001</v>
@@ -593,7 +639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:14">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>1002</v>
@@ -629,7 +675,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:14">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>2001</v>

--- a/Assets/Data/Excel/npc.xlsx
+++ b/Assets/Data/Excel/npc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cube\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E62F22F0-6FB8-4BAE-B4F1-67639D4600D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D29F86-6E6B-4898-A28B-271DA0096DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -233,7 +233,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -242,6 +242,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -638,6 +641,12 @@
       <c r="L5" s="2">
         <v>1</v>
       </c>
+      <c r="M5" s="4">
+        <v>100</v>
+      </c>
+      <c r="N5" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="2"/>
